--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059E2FB4-2734-4EF6-803A-4C3639FAA8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B642A0E6-001B-4A48-B5BF-9B61076A2847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7095" yWindow="0" windowWidth="21600" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="11">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -492,14 +492,14 @@
       </c>
       <c r="C6">
         <f>SUM(listening!C73:C102)</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>0.56666666666666665</v>
+        <v>0.73333333333333328</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -554,14 +554,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -578,7 +578,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1263,57 +1263,111 @@
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94">
+      <c r="A94" s="2">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
+      <c r="B94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95">
+      <c r="A95" s="2">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
+      <c r="B95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96">
+      <c r="A96" s="2">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
+      <c r="B98" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
+      <c r="B99" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
+      <c r="B100" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
+      <c r="B101" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>100</v>
+      </c>
+      <c r="B102" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1389,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1737,53 +1791,107 @@
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
+      <c r="B60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
+      </c>
+      <c r="B63" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3">

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B642A0E6-001B-4A48-B5BF-9B61076A2847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089293D7-3543-4D65-9F83-92364FAD052E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6840" yWindow="1485" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="13">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -89,6 +89,12 @@
   <si>
     <t>D</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -444,14 +450,14 @@
       </c>
       <c r="C3">
         <f>SUM(listening!C3:C12)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>10</v>
       </c>
       <c r="E3" s="1">
         <f>C3/D3</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -554,14 +560,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.375</v>
       </c>
     </row>
   </sheetData>
@@ -578,7 +584,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -596,10 +602,22 @@
       <c r="A3">
         <v>1</v>
       </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
         <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -607,47 +625,95 @@
         <f>A4+1</f>
         <v>3</v>
       </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
         <f t="shared" ref="A6:A69" si="0">A5+1</f>
         <v>4</v>
       </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1389,7 +1455,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1899,98 +1965,164 @@
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
+      <c r="B71" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
+      <c r="B73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
+      <c r="B74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089293D7-3543-4D65-9F83-92364FAD052E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4DADE5-8CA6-4164-87A1-A5754CCADF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6840" yWindow="1485" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="15">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -95,6 +95,12 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -466,14 +472,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0</v>
+        <v>0.23333333333333334</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -528,14 +534,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -584,7 +590,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -721,116 +727,176 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1455,7 +1521,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1472,6 +1538,12 @@
     <row r="3" spans="1:3">
       <c r="A3">
         <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1479,53 +1551,107 @@
         <f>A3+1</f>
         <v>102</v>
       </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
         <f t="shared" ref="A5:A68" si="0">A4+1</f>
         <v>103</v>
       </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4DADE5-8CA6-4164-87A1-A5754CCADF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58152AD-238F-4992-8A44-5DB6E5184441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6840" yWindow="1485" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11460" yWindow="0" windowWidth="18510" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="15">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -472,14 +472,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0.23333333333333334</v>
+        <v>0.53333333333333333</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -534,14 +534,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -590,7 +590,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -847,59 +847,119 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -1521,7 +1581,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1659,116 +1719,176 @@
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58152AD-238F-4992-8A44-5DB6E5184441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D770E178-5D48-4164-AFEA-7A04F718937E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11460" yWindow="0" windowWidth="18510" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="15">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -472,14 +472,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0.53333333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -488,14 +488,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.56666666666666665</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -534,14 +534,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.4</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -566,14 +566,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>46</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -962,193 +962,361 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-    </row>
-    <row r="56" spans="1:1">
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-    </row>
-    <row r="57" spans="1:1">
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-    </row>
-    <row r="58" spans="1:1">
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-    </row>
-    <row r="59" spans="1:1">
+      <c r="B58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-    </row>
-    <row r="60" spans="1:1">
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-    </row>
-    <row r="61" spans="1:1">
+      <c r="B60" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -1581,7 +1749,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1839,59 +2007,119 @@
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2343,128 +2571,176 @@
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
+      <c r="B75" t="s">
+        <v>9</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
+      <c r="B76" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
+      <c r="B77" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
+      <c r="B79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
+      <c r="B80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
+      <c r="B81" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D770E178-5D48-4164-AFEA-7A04F718937E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CA59EE-155E-4201-AD78-37038444AEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="15">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -534,14 +534,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.55000000000000004</v>
+        <v>0.72499999999999998</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -566,14 +566,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.625</v>
       </c>
     </row>
   </sheetData>
@@ -1749,7 +1749,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2127,59 +2127,119 @@
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
+      </c>
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2667,59 +2727,119 @@
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
+      <c r="B84" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
+      <c r="B85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
+      <c r="B86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
+      <c r="B87" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
+      <c r="B89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
+      <c r="B90" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
+      <c r="B91" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
+      </c>
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3">

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CA59EE-155E-4201-AD78-37038444AEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C568CD-3B9C-421B-826C-4D72FE14A861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="15">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -488,14 +488,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0.56666666666666665</v>
+        <v>0.76666666666666672</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -566,14 +566,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1303,35 +1303,71 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
+      <c r="B63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
+      <c r="B64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
+      <c r="B65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1749,7 +1785,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2847,56 +2883,86 @@
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
+      <c r="B93" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
+      <c r="B94" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
+      <c r="B95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C568CD-3B9C-421B-826C-4D72FE14A861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3009C63F-F7D5-4B1B-9487-F1A4278D7081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7275" yWindow="255" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="15">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -488,14 +488,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0.76666666666666672</v>
+        <v>0.93333333333333335</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -566,14 +566,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.6875</v>
+        <v>0.70833333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1375,17 +1375,35 @@
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1393,17 +1411,35 @@
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
       </c>
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
+      <c r="B71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1785,7 +1821,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2927,45 +2963,75 @@
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97">
+      <c r="A97" s="2">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="B97" t="s">
-        <v>8</v>
-      </c>
-      <c r="C97">
+      <c r="B97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98">
+      <c r="A98" s="2">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
+      <c r="B98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99">
+      <c r="A99" s="2">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
+      <c r="B99" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100">
+      <c r="A100" s="2">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
+      <c r="B100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101">
+      <c r="A101" s="2">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
+      <c r="B101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102">
+      <c r="A102" s="2">
         <f t="shared" si="1"/>
         <v>200</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3009C63F-F7D5-4B1B-9487-F1A4278D7081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96811EC-7D06-4F76-86EF-B2F879DD0275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7275" yWindow="255" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
     <sheet name="listening" sheetId="1" r:id="rId2"/>
     <sheet name="reading" sheetId="2" r:id="rId3"/>
+    <sheet name="review" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">listening!$A$2:$C$102</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="15">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -584,6 +588,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -604,7 +609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" hidden="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -626,7 +631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" hidden="1">
       <c r="A5">
         <f>A4+1</f>
         <v>3</v>
@@ -638,7 +643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" hidden="1">
       <c r="A6">
         <f t="shared" ref="A6:A69" si="0">A5+1</f>
         <v>4</v>
@@ -650,7 +655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" hidden="1">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -662,7 +667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" hidden="1">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -674,7 +679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" hidden="1">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -686,7 +691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" hidden="1">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -698,7 +703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" hidden="1">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -722,7 +727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" hidden="1">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -734,7 +739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" hidden="1">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -746,7 +751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" hidden="1">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -758,7 +763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" hidden="1">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -782,7 +787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" hidden="1">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -794,7 +799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" hidden="1">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -806,7 +811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" hidden="1">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -842,7 +847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" hidden="1">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -854,7 +859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" hidden="1">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -866,7 +871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" hidden="1">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -878,7 +883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" hidden="1">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -890,7 +895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" hidden="1">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -902,7 +907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" hidden="1">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -914,7 +919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" hidden="1">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -926,7 +931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" hidden="1">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -938,7 +943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" hidden="1">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -962,7 +967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" hidden="1">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -974,7 +979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" hidden="1">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -998,7 +1003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" hidden="1">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -1010,7 +1015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" hidden="1">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -1022,7 +1027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" hidden="1">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -1034,7 +1039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" hidden="1">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -1046,7 +1051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" hidden="1">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -1058,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" hidden="1">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -1082,7 +1087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" hidden="1">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -1094,7 +1099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" hidden="1">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -1106,7 +1111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" hidden="1">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -1118,7 +1123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" hidden="1">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -1130,7 +1135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" hidden="1">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -1142,7 +1147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" hidden="1">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -1154,7 +1159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" hidden="1">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -1166,7 +1171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" hidden="1">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -1178,7 +1183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" hidden="1">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -1202,7 +1207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" hidden="1">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -1214,7 +1219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" hidden="1">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -1226,7 +1231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" hidden="1">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -1238,7 +1243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" hidden="1">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -1250,7 +1255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" hidden="1">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -1262,7 +1267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" hidden="1">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -1274,7 +1279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" hidden="1">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -1286,7 +1291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" hidden="1">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -1298,7 +1303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" hidden="1">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -1310,7 +1315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" hidden="1">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -1322,7 +1327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" hidden="1">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -1334,7 +1339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" hidden="1">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -1346,7 +1351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" hidden="1">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -1358,7 +1363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" hidden="1">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -1382,7 +1387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" hidden="1">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -1394,7 +1399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" hidden="1">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -1406,7 +1411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" hidden="1">
       <c r="A70">
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
@@ -1418,7 +1423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" hidden="1">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -1430,7 +1435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" hidden="1">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -1454,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" hidden="1">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -1466,7 +1471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" hidden="1">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -1478,7 +1483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" hidden="1">
       <c r="A76" s="2">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -1514,7 +1519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" hidden="1">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -1526,7 +1531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" hidden="1">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -1538,7 +1543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" hidden="1">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -1550,7 +1555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" hidden="1">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -1562,7 +1567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" hidden="1">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -1574,7 +1579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" hidden="1">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -1586,7 +1591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" hidden="1">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -1610,7 +1615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" hidden="1">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -1622,7 +1627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" hidden="1">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -1634,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" hidden="1">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -1646,7 +1651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" hidden="1">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -1658,7 +1663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" hidden="1">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -1670,7 +1675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" hidden="1">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -1682,7 +1687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" hidden="1">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -1694,7 +1699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" hidden="1">
       <c r="A94" s="2">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -1730,7 +1735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" hidden="1">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -1754,7 +1759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" hidden="1">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -1766,7 +1771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" hidden="1">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -1790,7 +1795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" hidden="1">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -1803,6 +1808,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:C102" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B102" xr:uid="{14B9F633-8D16-4C6A-BDBF-F784015327B4}">
@@ -3043,4 +3055,253 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
+  <dimension ref="A2:C26"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>92</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>93</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>101</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>108</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>111</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>114</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>125</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>126</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>127</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>130</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B26" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+      <formula1>"A,B,C,D"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96811EC-7D06-4F76-86EF-B2F879DD0275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEA1FD4-F9AB-48D7-A2A0-D74278CEFB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="15">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3059,7 +3059,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C26"/>
+  <dimension ref="A2:C32"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3262,43 +3262,151 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>19</v>
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>30</v>
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>133</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>135</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>136</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>138</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B26" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B32" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47164274-5883-4E13-9429-29CDFE7F445F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F315B50B-99CF-491D-BF6C-F47F61CBBBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11280" yWindow="0" windowWidth="18015" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="135" yWindow="240" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="23">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -122,6 +122,22 @@
     <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -143,18 +159,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -169,10 +179,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -524,14 +533,14 @@
       </c>
       <c r="C6">
         <f>SUM(listening!C73:C102)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -586,14 +595,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.20833333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -610,7 +619,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1107,156 +1116,270 @@
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
+      <c r="B73" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
+      <c r="B74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
+      <c r="B75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="2">
+      <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
+      <c r="B76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="2">
+      <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
+      <c r="B77" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="2">
+      <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
+      <c r="B78" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
+      <c r="B79" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
+      <c r="B80" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
+      <c r="B82" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
+      <c r="B83" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
+      <c r="B84" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
+      <c r="B85" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
+      <c r="B86" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
+      <c r="B87" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
+      <c r="B89" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
+      <c r="B90" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
+      <c r="B91" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
+      <c r="B92" t="s">
+        <v>22</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
+      <c r="B93" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="2">
+      <c r="A94">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="2">
+      <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="2">
+      <c r="A96">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
@@ -1314,7 +1437,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1855,149 +1978,197 @@
         <v>178</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
-    </row>
-    <row r="94" spans="1:1">
+      <c r="B93" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
-    </row>
-    <row r="95" spans="1:1">
+      <c r="B94" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
-    </row>
-    <row r="96" spans="1:1">
+      <c r="B95" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
+      <c r="B96" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="2">
+      <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
+      <c r="B97" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="2">
+      <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
+      <c r="B98" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="2">
+      <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
+      <c r="B99" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="2">
+      <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
+      <c r="B100" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="2">
+      <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
+      <c r="B101" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="2">
+      <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
+      <c r="B102" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F315B50B-99CF-491D-BF6C-F47F61CBBBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F999FECA-A652-48CD-9F37-77E7A6E0056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="240" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -136,6 +136,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -533,14 +549,14 @@
       </c>
       <c r="C6">
         <f>SUM(listening!C73:C102)</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>0.6333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -563,14 +579,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -619,7 +635,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1368,53 +1384,107 @@
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
+      <c r="B94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
+      <c r="B95" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>23</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
+      <c r="B98" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
+      <c r="B99" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
+      <c r="B100" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
+      <c r="B101" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>100</v>
+      </c>
+      <c r="B102" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1507,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1575,116 +1645,176 @@
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F999FECA-A652-48CD-9F37-77E7A6E0056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9AD557-2D18-4CB1-B365-B3DEB9B676EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="495" yWindow="0" windowWidth="16605" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="27">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -517,14 +517,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -579,14 +579,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.4</v>
+        <v>0.57499999999999996</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -635,7 +635,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -772,116 +772,176 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1507,7 +1567,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1765,59 +1825,119 @@
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9AD557-2D18-4CB1-B365-B3DEB9B676EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE9571A-7E1A-44C1-BCED-281539970785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="495" yWindow="0" windowWidth="16605" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14715" yWindow="495" windowWidth="13680" windowHeight="13575" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="29">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -152,6 +152,14 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>as for</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>～のため</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -517,14 +525,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0.33333333333333331</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -579,14 +587,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.57499999999999996</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -635,7 +643,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -892,59 +900,119 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -1561,13 +1629,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1940,97 +2008,163 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:6">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:6">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:6">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:6">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:6">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:6">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE9571A-7E1A-44C1-BCED-281539970785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E8D417-1296-4337-9F08-481D2B4AF5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14715" yWindow="495" windowWidth="13680" windowHeight="13575" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15270" yWindow="0" windowWidth="13680" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="29">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -525,14 +525,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -603,14 +603,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -643,7 +643,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1015,97 +1015,157 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -1635,7 +1695,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2139,128 +2199,200 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E8D417-1296-4337-9F08-481D2B4AF5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55865E4-D9F1-4C28-8EB0-98E4AFA87012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15270" yWindow="0" windowWidth="13680" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -160,6 +160,18 @@
   </si>
   <si>
     <t>～のため</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -541,14 +553,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.23333333333333334</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -619,14 +631,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.20833333333333334</v>
+        <v>0.39583333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +655,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1140,128 +1152,182 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -1695,7 +1761,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2343,53 +2409,107 @@
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
+      <c r="B60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
+      </c>
+      <c r="B63" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3">

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55865E4-D9F1-4C28-8EB0-98E4AFA87012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FDBFBC-41D5-4565-A9BF-2129D60EE5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4920" yWindow="1305" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="35">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -172,6 +172,18 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -553,14 +565,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0.23333333333333334</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -631,14 +643,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.39583333333333331</v>
+        <v>0.70833333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -655,7 +667,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1260,71 +1272,143 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
+      <c r="B55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
+      <c r="B61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
+      <c r="B62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1761,7 +1845,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2517,101 +2601,203 @@
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
+      <c r="B66" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
+      <c r="B68" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
+      <c r="B72" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
+      <c r="B73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
+      <c r="B74" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
+      <c r="B75" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
+      <c r="B77" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
+      </c>
+      <c r="B80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2619,11 +2805,23 @@
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
+      <c r="B81" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:3">

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FDBFBC-41D5-4565-A9BF-2129D60EE5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C607C6C2-E370-429C-97E7-031FA900CDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="1305" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="39">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -184,6 +184,22 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -565,14 +581,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0.6333333333333333</v>
+        <v>0.93333333333333335</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -643,14 +659,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.70833333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -667,7 +683,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1416,35 +1432,71 @@
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
+      <c r="B64" t="s">
+        <v>36</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
+      <c r="B65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
+      <c r="B66" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
+      <c r="B67" t="s">
+        <v>38</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
+      <c r="B68" t="s">
+        <v>37</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>35</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1452,17 +1504,35 @@
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
       </c>
+      <c r="B70" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
+      <c r="B71" t="s">
+        <v>38</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1845,7 +1915,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2829,59 +2899,119 @@
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
+      <c r="B83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
+      <c r="B84" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
+      <c r="B85" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
+      <c r="B86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
+      <c r="B87" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
+      <c r="B89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
+      <c r="B90" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
+      <c r="B91" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
+      </c>
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3">

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C607C6C2-E370-429C-97E7-031FA900CDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300E4583-19F2-4149-A59B-4CD576014E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="75" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">listening!$A$2:$C$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">reading!$A$2:$F$102</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="39">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -223,12 +224,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -243,9 +250,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -677,6 +685,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -697,7 +706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" hidden="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -708,7 +717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" hidden="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -719,7 +728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" hidden="1">
       <c r="A5">
         <f>A4+1</f>
         <v>3</v>
@@ -731,7 +740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" hidden="1">
       <c r="A6">
         <f t="shared" ref="A6:A69" si="0">A5+1</f>
         <v>4</v>
@@ -743,7 +752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" hidden="1">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -755,7 +764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" hidden="1">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -767,7 +776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" hidden="1">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -779,7 +788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" hidden="1">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -791,7 +800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" hidden="1">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -803,7 +812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" hidden="1">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -815,7 +824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" hidden="1">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -827,7 +836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" hidden="1">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -839,7 +848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" hidden="1">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -851,7 +860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" hidden="1">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -863,7 +872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" hidden="1">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -875,7 +884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" hidden="1">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -887,7 +896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" hidden="1">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -899,7 +908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" hidden="1">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -911,7 +920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" hidden="1">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -923,7 +932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" hidden="1">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -935,7 +944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" hidden="1">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -947,7 +956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" hidden="1">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -959,7 +968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" hidden="1">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -971,7 +980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" hidden="1">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -983,7 +992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" hidden="1">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -995,7 +1004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" hidden="1">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1008,30 +1017,30 @@
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29">
+      <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30">
+      <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1043,7 +1052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" hidden="1">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1055,7 +1064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" hidden="1">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1067,7 +1076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" hidden="1">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -1080,90 +1089,90 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35">
+      <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36">
+      <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37">
+      <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38">
+      <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39">
+      <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40">
+      <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41">
+      <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="C41" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -1175,7 +1184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" hidden="1">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -1187,7 +1196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" hidden="1">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -1200,18 +1209,18 @@
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45">
+      <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="C45" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" hidden="1">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -1223,7 +1232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" hidden="1">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -1235,7 +1244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" hidden="1">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -1247,7 +1256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" hidden="1">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -1260,18 +1269,18 @@
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50">
+      <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="C50" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -1283,7 +1292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" hidden="1">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -1295,7 +1304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" hidden="1">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -1307,7 +1316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" hidden="1">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -1319,7 +1328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" hidden="1">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -1331,7 +1340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" hidden="1">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -1343,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" hidden="1">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -1355,7 +1364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" hidden="1">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -1367,7 +1376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" hidden="1">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -1379,7 +1388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" hidden="1">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -1391,7 +1400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" hidden="1">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -1403,7 +1412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" hidden="1">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -1415,7 +1424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" hidden="1">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -1427,7 +1436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" hidden="1">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -1439,7 +1448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" hidden="1">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -1451,7 +1460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" hidden="1">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -1463,7 +1472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" hidden="1">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -1475,7 +1484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" hidden="1">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -1487,7 +1496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" hidden="1">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -1499,7 +1508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" hidden="1">
       <c r="A70">
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
@@ -1511,7 +1520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" hidden="1">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -1523,7 +1532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" hidden="1">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -1535,7 +1544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" hidden="1">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -1547,7 +1556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" hidden="1">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -1559,7 +1568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" hidden="1">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -1571,7 +1580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" hidden="1">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -1583,7 +1592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" hidden="1">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -1595,7 +1604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" hidden="1">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -1607,7 +1616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" hidden="1">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -1619,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" hidden="1">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -1632,18 +1641,18 @@
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81">
+      <c r="A81" s="2">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="C81" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" hidden="1">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -1655,7 +1664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" hidden="1">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -1667,7 +1676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" hidden="1">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -1679,7 +1688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" hidden="1">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -1691,7 +1700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" hidden="1">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -1703,7 +1712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" hidden="1">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -1715,7 +1724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" hidden="1">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -1727,7 +1736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" hidden="1">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -1739,7 +1748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" hidden="1">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -1751,7 +1760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" hidden="1">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -1763,7 +1772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" hidden="1">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -1776,18 +1785,18 @@
       </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93">
+      <c r="A93" s="2">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="C93" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" hidden="1">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -1799,7 +1808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" hidden="1">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -1812,18 +1821,18 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96">
+      <c r="A96" s="2">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
+      <c r="C96" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" hidden="1">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -1836,18 +1845,18 @@
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98">
+      <c r="A98" s="2">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
+      <c r="C98" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" hidden="1">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -1859,7 +1868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" hidden="1">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -1871,7 +1880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" hidden="1">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -1883,7 +1892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" hidden="1">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -1896,7 +1905,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:C102" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B102" xr:uid="{14B9F633-8D16-4C6A-BDBF-F784015327B4}">
@@ -1909,6 +1924,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -1929,7 +1945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" hidden="1">
       <c r="A3">
         <v>101</v>
       </c>
@@ -1940,7 +1956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" hidden="1">
       <c r="A4">
         <f>A3+1</f>
         <v>102</v>
@@ -1952,7 +1968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" hidden="1">
       <c r="A5">
         <f t="shared" ref="A5:A68" si="0">A4+1</f>
         <v>103</v>
@@ -1964,7 +1980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" hidden="1">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
@@ -2000,7 +2016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" hidden="1">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>107</v>
@@ -2012,7 +2028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" hidden="1">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108</v>
@@ -2024,7 +2040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" hidden="1">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
@@ -2036,7 +2052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" hidden="1">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
@@ -2048,7 +2064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" hidden="1">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>111</v>
@@ -2060,7 +2076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" hidden="1">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
@@ -2072,7 +2088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" hidden="1">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
@@ -2084,7 +2100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" hidden="1">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
@@ -2096,7 +2112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" hidden="1">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
@@ -2108,7 +2124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" hidden="1">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
@@ -2120,7 +2136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" hidden="1">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>117</v>
@@ -2156,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" hidden="1">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
@@ -2168,7 +2184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" hidden="1">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
@@ -2180,7 +2196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" hidden="1">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
@@ -2192,7 +2208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" hidden="1">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
@@ -2216,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" hidden="1">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
@@ -2228,7 +2244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" hidden="1">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
@@ -2240,7 +2256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" hidden="1">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
@@ -2252,7 +2268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" hidden="1">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
@@ -2288,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" hidden="1">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
@@ -2354,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" hidden="1">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
@@ -2378,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" hidden="1">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
@@ -2414,7 +2430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" hidden="1">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
@@ -2438,7 +2454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" hidden="1">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
@@ -2450,7 +2466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" hidden="1">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
@@ -2462,7 +2478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" hidden="1">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
@@ -2474,7 +2490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" hidden="1">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
@@ -2486,7 +2502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" hidden="1">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
@@ -2498,7 +2514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" hidden="1">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
@@ -2510,7 +2526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" hidden="1">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
@@ -2522,7 +2538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" hidden="1">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
@@ -2534,7 +2550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" hidden="1">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
@@ -2546,7 +2562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" hidden="1">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
@@ -2558,7 +2574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" hidden="1">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
@@ -2570,7 +2586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" hidden="1">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
@@ -2582,7 +2598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" hidden="1">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
@@ -2594,7 +2610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" hidden="1">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
@@ -2606,7 +2622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" hidden="1">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
@@ -2618,7 +2634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" hidden="1">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
@@ -2630,7 +2646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" hidden="1">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
@@ -2642,7 +2658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" hidden="1">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
@@ -2654,7 +2670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" hidden="1">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
@@ -2666,7 +2682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" hidden="1">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
@@ -2690,7 +2706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" hidden="1">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
@@ -2714,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" hidden="1">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
@@ -2738,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" hidden="1">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
@@ -2750,7 +2766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" hidden="1">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
@@ -2762,7 +2778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" hidden="1">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
@@ -2774,7 +2790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" hidden="1">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
@@ -2786,7 +2802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" hidden="1">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
@@ -2798,7 +2814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" hidden="1">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
@@ -2810,7 +2826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" hidden="1">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
@@ -2822,7 +2838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" hidden="1">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
@@ -2834,7 +2850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" hidden="1">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
@@ -2846,7 +2862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" hidden="1">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
@@ -2858,7 +2874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" hidden="1">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
@@ -2870,7 +2886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" hidden="1">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
@@ -2906,7 +2922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" hidden="1">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
@@ -2918,7 +2934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" hidden="1">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
@@ -2930,7 +2946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" hidden="1">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
@@ -2978,7 +2994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" hidden="1">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
@@ -2990,7 +3006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" hidden="1">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
@@ -3002,7 +3018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" hidden="1">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
@@ -3014,7 +3030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" hidden="1">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
@@ -3026,7 +3042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" hidden="1">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
@@ -3038,7 +3054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" hidden="1">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
@@ -3050,7 +3066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" hidden="1">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
@@ -3062,7 +3078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" hidden="1">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
@@ -3074,7 +3090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" hidden="1">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
@@ -3086,7 +3102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" hidden="1">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
@@ -3098,7 +3114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" hidden="1">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
@@ -3110,7 +3126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" hidden="1">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
@@ -3122,7 +3138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" hidden="1">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
@@ -3135,6 +3151,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:F102" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B102" xr:uid="{507A3D4C-54A2-49AD-8DD6-62E0792701B4}">
@@ -3147,7 +3170,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C32"/>
+  <dimension ref="A2:C15"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3162,153 +3185,146 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3">
-        <v>74</v>
+      <c r="A3" s="2">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4">
-        <v>75</v>
+      <c r="A4" s="2">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5">
-        <v>76</v>
+      <c r="A5" s="2">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6">
-        <v>92</v>
+      <c r="A6" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7">
-        <v>93</v>
+      <c r="A7" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8">
-        <v>94</v>
+      <c r="A8" s="2">
+        <v>38</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9">
-        <v>83</v>
+      <c r="A9" s="2">
+        <v>39</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10">
-        <v>84</v>
+      <c r="A10" s="2">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11">
-        <v>85</v>
+      <c r="A11" s="2">
+        <v>36</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>101</v>
+        <v>105</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>108</v>
+        <v>106</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>111</v>
+        <v>118</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32">
-        <v>138</v>
+        <v>119</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300E4583-19F2-4149-A59B-4CD576014E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A34B9E-EC12-47A2-B830-CEB8535BC88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="75" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="39">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -250,10 +250,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3170,7 +3171,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C15"/>
+  <dimension ref="A2:C27"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3284,47 +3285,179 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12">
+      <c r="A12" s="3">
         <v>105</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13">
+      <c r="A13" s="3">
         <v>106</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14">
+      <c r="A14" s="3">
         <v>118</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15">
+      <c r="A15" s="3">
         <v>119</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15">
-        <v>1</v>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3">
+        <v>42</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3">
+        <v>43</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3">
+        <v>47</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3">
+        <v>48</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3">
+        <v>49</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>124</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>129</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>130</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>132</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>133</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>134</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A34B9E-EC12-47A2-B830-CEB8535BC88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4510C7A9-B10C-46C4-855D-A3DDCC88A205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="75" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="39">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -250,11 +250,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3171,7 +3170,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C27"/>
+  <dimension ref="A2:C39"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3285,112 +3284,112 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="3">
+      <c r="A12">
         <v>105</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="3">
+      <c r="A13">
         <v>106</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="3">
+      <c r="A14">
         <v>118</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3">
+      <c r="A15">
         <v>119</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="3">
+      <c r="A16">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="3">
+      <c r="A17">
         <v>42</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3">
+      <c r="A18">
         <v>43</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="3">
+      <c r="A19">
         <v>47</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="3">
+      <c r="A20">
         <v>48</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="3">
+      <c r="A21">
         <v>49</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21">
         <v>1</v>
       </c>
     </row>
@@ -3398,10 +3397,10 @@
       <c r="A22">
         <v>124</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="3">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22">
         <v>1</v>
       </c>
     </row>
@@ -3409,10 +3408,10 @@
       <c r="A23">
         <v>129</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="3">
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23">
         <v>0</v>
       </c>
     </row>
@@ -3420,10 +3419,10 @@
       <c r="A24">
         <v>130</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24">
         <v>1</v>
       </c>
     </row>
@@ -3431,10 +3430,10 @@
       <c r="A25">
         <v>132</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25">
         <v>0</v>
       </c>
     </row>
@@ -3442,10 +3441,10 @@
       <c r="A26">
         <v>133</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26">
         <v>1</v>
       </c>
     </row>
@@ -3453,17 +3452,149 @@
       <c r="A27">
         <v>134</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>77</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>78</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>91</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>135</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>137</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>139</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>141</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>142</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>143</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B32" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B32 B34:B36" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>

--- a/toeic-test-v4/trial1-v1.xlsx
+++ b/toeic-test-v4/trial1-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4510C7A9-B10C-46C4-855D-A3DDCC88A205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D85958-FE7F-45B2-A720-BE6159927A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="75" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="39">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3170,7 +3170,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C39"/>
+  <dimension ref="A2:C52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3589,6 +3589,149 @@
       </c>
       <c r="C39">
         <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>93</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>94</v>
+      </c>
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>95</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>96</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>162</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>163</v>
+      </c>
+      <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>164</v>
+      </c>
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>165</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>166</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>167</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>168</v>
+      </c>
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
